--- a/artfynd/A 24072-2022 artfynd.xlsx
+++ b/artfynd/A 24072-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24072-2022 artfynd.xlsx
+++ b/artfynd/A 24072-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103088344</v>
+        <v>103088338</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675248.7911085174</v>
+        <v>675357</v>
       </c>
       <c r="R2" t="n">
-        <v>7394572.133132589</v>
+        <v>7394594</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103088327</v>
+        <v>103088324</v>
       </c>
       <c r="B3" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675459.2640108957</v>
+        <v>675415</v>
       </c>
       <c r="R3" t="n">
-        <v>7394454.063592484</v>
+        <v>7394540</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +872,7 @@
         <v>103088337</v>
       </c>
       <c r="B4" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>675287.7939198865</v>
+        <v>675288</v>
       </c>
       <c r="R4" t="n">
-        <v>7394717.605882816</v>
+        <v>7394718</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103088329</v>
+        <v>103088341</v>
       </c>
       <c r="B5" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675472.3078679317</v>
+        <v>675261</v>
       </c>
       <c r="R5" t="n">
-        <v>7394443.341341253</v>
+        <v>7394681</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103088336</v>
+        <v>103088353</v>
       </c>
       <c r="B6" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675281.635567802</v>
+        <v>675298</v>
       </c>
       <c r="R6" t="n">
-        <v>7394745.493845763</v>
+        <v>7394603</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1131,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103088347</v>
+        <v>103088357</v>
       </c>
       <c r="B7" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>675264.5825769593</v>
+        <v>675446</v>
       </c>
       <c r="R7" t="n">
-        <v>7394593.450912395</v>
+        <v>7394523</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,19 +1228,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103088332</v>
+        <v>103088334</v>
       </c>
       <c r="B8" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675479.5710607558</v>
+        <v>675166</v>
       </c>
       <c r="R8" t="n">
-        <v>7394429.462911145</v>
+        <v>7394884</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1420,19 +1325,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103088334</v>
+        <v>103088331</v>
       </c>
       <c r="B9" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>675165.5641502885</v>
+        <v>675474</v>
       </c>
       <c r="R9" t="n">
-        <v>7394884.29088799</v>
+        <v>7394435</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1532,19 +1422,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103088331</v>
+        <v>103088345</v>
       </c>
       <c r="B10" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>675474.4265226482</v>
+        <v>675264</v>
       </c>
       <c r="R10" t="n">
-        <v>7394435.110847594</v>
+        <v>7394594</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1644,19 +1519,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103088353</v>
+        <v>103088329</v>
       </c>
       <c r="B11" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>675298.2826955639</v>
+        <v>675472</v>
       </c>
       <c r="R11" t="n">
-        <v>7394602.762285368</v>
+        <v>7394443</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1756,19 +1616,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103088350</v>
+        <v>103088336</v>
       </c>
       <c r="B12" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>675312.932638778</v>
+        <v>675282</v>
       </c>
       <c r="R12" t="n">
-        <v>7394623.210998402</v>
+        <v>7394746</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1868,19 +1713,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103088355</v>
+        <v>103088325</v>
       </c>
       <c r="B13" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>675298.6922788277</v>
+        <v>675503</v>
       </c>
       <c r="R13" t="n">
-        <v>7394564.947718199</v>
+        <v>7394469</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1980,19 +1810,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103314193</v>
+        <v>103088343</v>
       </c>
       <c r="B14" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,40 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>NO om Piertinjaure, Lu lm</t>
+          <t>NV Piertinjaure, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>675481.3987679164</v>
+        <v>675223</v>
       </c>
       <c r="R14" t="n">
-        <v>7394438.342821089</v>
+        <v>7394622</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2095,65 +1907,39 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>S101</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Pia Edfors, Elin Götmark, Carin von Köhler, Linda Hanson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103088342</v>
+        <v>103314193</v>
       </c>
       <c r="B15" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,37 +1947,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NV Piertinjaure, Lu lm</t>
+          <t>NO om Piertinjaure, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>675246.6435011048</v>
+        <v>675481</v>
       </c>
       <c r="R15" t="n">
-        <v>7394662.414479464</v>
+        <v>7394438</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2218,76 +2007,72 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>S101</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Pia Edfors, Elin Götmark, Carin von Köhler, Linda Hanson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103088343</v>
+        <v>103088327</v>
       </c>
       <c r="B16" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2297,10 +2082,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>675223.2999518961</v>
+        <v>675459</v>
       </c>
       <c r="R16" t="n">
-        <v>7394621.896754115</v>
+        <v>7394454</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2330,19 +2115,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,15 +2144,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103088348</v>
+        <v>103088332</v>
       </c>
       <c r="B17" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2385,21 +2155,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2409,10 +2179,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>675283.8851013245</v>
+        <v>675480</v>
       </c>
       <c r="R17" t="n">
-        <v>7394628.534537223</v>
+        <v>7394429</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2442,19 +2212,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,15 +2241,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103088356</v>
+        <v>103088342</v>
       </c>
       <c r="B18" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2521,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>675331.3648710318</v>
+        <v>675247</v>
       </c>
       <c r="R18" t="n">
-        <v>7394609.246552898</v>
+        <v>7394662</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2554,19 +2309,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,15 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103088359</v>
+        <v>103088344</v>
       </c>
       <c r="B19" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>675429.4517976006</v>
+        <v>675249</v>
       </c>
       <c r="R19" t="n">
-        <v>7394452.565749522</v>
+        <v>7394572</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2666,19 +2406,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,15 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103088324</v>
+        <v>103088348</v>
       </c>
       <c r="B20" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2721,21 +2446,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2745,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>675415.0878636641</v>
+        <v>675284</v>
       </c>
       <c r="R20" t="n">
-        <v>7394540.481395717</v>
+        <v>7394629</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2778,19 +2503,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,15 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103088341</v>
+        <v>103088350</v>
       </c>
       <c r="B21" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,21 +2543,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2857,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>675261.4447063812</v>
+        <v>675313</v>
       </c>
       <c r="R21" t="n">
-        <v>7394680.482241984</v>
+        <v>7394623</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2890,19 +2600,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,37 +2629,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103088354</v>
+        <v>103088356</v>
       </c>
       <c r="B22" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2969,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>675298.6922788277</v>
+        <v>675331</v>
       </c>
       <c r="R22" t="n">
-        <v>7394564.947718199</v>
+        <v>7394609</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3002,19 +2697,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,37 +2726,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103088338</v>
+        <v>103088359</v>
       </c>
       <c r="B23" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3081,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>675357.469045809</v>
+        <v>675429</v>
       </c>
       <c r="R23" t="n">
-        <v>7394593.778271778</v>
+        <v>7394453</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3114,19 +2794,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3153,37 +2823,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103088357</v>
+        <v>103088354</v>
       </c>
       <c r="B24" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3193,10 +2858,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>675446.5075343533</v>
+        <v>675299</v>
       </c>
       <c r="R24" t="n">
-        <v>7394522.961460182</v>
+        <v>7394565</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3226,19 +2891,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,37 +2920,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103088345</v>
+        <v>103088347</v>
       </c>
       <c r="B25" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3305,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>675264.5825769593</v>
+        <v>675264</v>
       </c>
       <c r="R25" t="n">
-        <v>7394593.450912395</v>
+        <v>7394594</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3338,19 +2988,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3374,6 +3014,103 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>103088355</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NV Piertinjaure, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>675299</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7394565</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Pia Edfors, Elin Götmark, Carin von Köhler, Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24072-2022 artfynd.xlsx
+++ b/artfynd/A 24072-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088338</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088324</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088337</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088341</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088353</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088357</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088334</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088331</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088345</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088329</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088336</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088325</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088343</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103314193</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2141,6 +2216,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088327</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2238,6 +2318,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088332</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2335,6 +2420,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088342</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2432,6 +2522,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088344</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2529,6 +2624,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088348</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2626,6 +2726,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088350</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2723,6 +2828,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088356</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2820,6 +2930,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088359</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2917,6 +3032,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088354</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3014,6 +3134,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088347</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3111,8 +3236,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103088355</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>